--- a/data/nzd0192/nzd0192.xlsx
+++ b/data/nzd0192/nzd0192.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M699"/>
+  <dimension ref="A1:M701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31903,6 +31903,96 @@
       <c r="M699" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:00:08+00:00</t>
+        </is>
+      </c>
+      <c r="B700" t="n">
+        <v>339.52</v>
+      </c>
+      <c r="C700" t="n">
+        <v>337.43</v>
+      </c>
+      <c r="D700" t="n">
+        <v>343.95</v>
+      </c>
+      <c r="E700" t="n">
+        <v>345.33</v>
+      </c>
+      <c r="F700" t="n">
+        <v>348.69</v>
+      </c>
+      <c r="G700" t="n">
+        <v>357.63</v>
+      </c>
+      <c r="H700" t="n">
+        <v>368.78</v>
+      </c>
+      <c r="I700" t="n">
+        <v>363.84</v>
+      </c>
+      <c r="J700" t="n">
+        <v>362.13</v>
+      </c>
+      <c r="K700" t="n">
+        <v>352.57</v>
+      </c>
+      <c r="L700" t="n">
+        <v>348.57</v>
+      </c>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B701" t="n">
+        <v>338.55</v>
+      </c>
+      <c r="C701" t="n">
+        <v>336.82</v>
+      </c>
+      <c r="D701" t="n">
+        <v>342.97</v>
+      </c>
+      <c r="E701" t="n">
+        <v>343.45</v>
+      </c>
+      <c r="F701" t="n">
+        <v>347.15</v>
+      </c>
+      <c r="G701" t="n">
+        <v>355.6</v>
+      </c>
+      <c r="H701" t="n">
+        <v>368.09</v>
+      </c>
+      <c r="I701" t="n">
+        <v>362.49</v>
+      </c>
+      <c r="J701" t="n">
+        <v>361.94</v>
+      </c>
+      <c r="K701" t="n">
+        <v>352.98</v>
+      </c>
+      <c r="L701" t="n">
+        <v>348.32</v>
+      </c>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -31917,7 +32007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B709"/>
+  <dimension ref="A1:B711"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39010,6 +39100,26 @@
       </c>
       <c r="B709" t="n">
         <v>0.29</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B710" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B711" t="n">
+        <v>-0.41</v>
       </c>
     </row>
   </sheetData>
@@ -39178,28 +39288,28 @@
         <v>0.1845</v>
       </c>
       <c r="I2" t="n">
-        <v>0.165961155552959</v>
+        <v>0.1637785670278611</v>
       </c>
       <c r="J2" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="K2" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05482263545268706</v>
+        <v>0.05369974446026315</v>
       </c>
       <c r="M2" t="n">
-        <v>4.069674395860257</v>
+        <v>4.068764805213444</v>
       </c>
       <c r="N2" t="n">
-        <v>25.8648839235137</v>
+        <v>25.83327992903433</v>
       </c>
       <c r="O2" t="n">
-        <v>5.085753034066214</v>
+        <v>5.082644973735066</v>
       </c>
       <c r="P2" t="n">
-        <v>338.4981290993804</v>
+        <v>338.5209258801421</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -39256,28 +39366,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3466586326438993</v>
+        <v>0.3430123185983322</v>
       </c>
       <c r="J3" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="K3" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1294331139688319</v>
+        <v>0.1274667898291936</v>
       </c>
       <c r="M3" t="n">
-        <v>5.489654699186387</v>
+        <v>5.491959737255213</v>
       </c>
       <c r="N3" t="n">
-        <v>44.02557265712935</v>
+        <v>44.01624896053599</v>
       </c>
       <c r="O3" t="n">
-        <v>6.63517691227064</v>
+        <v>6.63447427913742</v>
       </c>
       <c r="P3" t="n">
-        <v>334.3965799335855</v>
+        <v>334.4346623687329</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39334,28 +39444,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2507297237926477</v>
+        <v>0.2492450530098429</v>
       </c>
       <c r="J4" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="K4" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09855928420873072</v>
+        <v>0.09800242499076695</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6321584390059</v>
+        <v>4.625980895767838</v>
       </c>
       <c r="N4" t="n">
-        <v>31.31810705307953</v>
+        <v>31.24858238804958</v>
       </c>
       <c r="O4" t="n">
-        <v>5.596258308287737</v>
+        <v>5.590043147243998</v>
       </c>
       <c r="P4" t="n">
-        <v>339.4588126272905</v>
+        <v>339.4743206585111</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39412,28 +39522,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3086868407776109</v>
+        <v>0.306000975078249</v>
       </c>
       <c r="J5" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="K5" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1355279273746725</v>
+        <v>0.1339855438522073</v>
       </c>
       <c r="M5" t="n">
-        <v>4.566533097626992</v>
+        <v>4.564731697011801</v>
       </c>
       <c r="N5" t="n">
-        <v>33.10568919070118</v>
+        <v>33.07664839368073</v>
       </c>
       <c r="O5" t="n">
-        <v>5.75375435613141</v>
+        <v>5.751230163511171</v>
       </c>
       <c r="P5" t="n">
-        <v>340.9745074372432</v>
+        <v>341.0025627171497</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39490,28 +39600,28 @@
         <v>0.1235</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2908907885118427</v>
+        <v>0.2880852017671739</v>
       </c>
       <c r="J6" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="K6" t="n">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1118034921444294</v>
+        <v>0.1103166182721725</v>
       </c>
       <c r="M6" t="n">
-        <v>5.049308241349058</v>
+        <v>5.050496450071545</v>
       </c>
       <c r="N6" t="n">
-        <v>36.43740635972316</v>
+        <v>36.40314899857991</v>
       </c>
       <c r="O6" t="n">
-        <v>6.036340477451811</v>
+        <v>6.033502216671501</v>
       </c>
       <c r="P6" t="n">
-        <v>345.1663679566664</v>
+        <v>345.1957743409239</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39568,28 +39678,28 @@
         <v>0.1494</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1697177466636618</v>
+        <v>0.1680974869303976</v>
       </c>
       <c r="J7" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="K7" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06051303826189092</v>
+        <v>0.05972109167030082</v>
       </c>
       <c r="M7" t="n">
-        <v>4.097902816913327</v>
+        <v>4.094580089678516</v>
       </c>
       <c r="N7" t="n">
-        <v>24.35793925368033</v>
+        <v>24.31420510304478</v>
       </c>
       <c r="O7" t="n">
-        <v>4.935376303148558</v>
+        <v>4.930943632109861</v>
       </c>
       <c r="P7" t="n">
-        <v>354.9884239898765</v>
+        <v>355.0053508601869</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39646,28 +39756,28 @@
         <v>0.1153</v>
       </c>
       <c r="I8" t="n">
-        <v>0.15045852617091</v>
+        <v>0.1512280256635285</v>
       </c>
       <c r="J8" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="K8" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="L8" t="n">
-        <v>0.034186957929627</v>
+        <v>0.0347284769425803</v>
       </c>
       <c r="M8" t="n">
-        <v>4.655827003349067</v>
+        <v>4.64562112340172</v>
       </c>
       <c r="N8" t="n">
-        <v>34.83456930118831</v>
+        <v>34.74057475229837</v>
       </c>
       <c r="O8" t="n">
-        <v>5.902081776897734</v>
+        <v>5.894113567984449</v>
       </c>
       <c r="P8" t="n">
-        <v>363.1178435200888</v>
+        <v>363.1098090410278</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -39724,28 +39834,28 @@
         <v>0.1881</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09814760209999625</v>
+        <v>0.09836584439830896</v>
       </c>
       <c r="J9" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="K9" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02193959252846645</v>
+        <v>0.02216823594093331</v>
       </c>
       <c r="M9" t="n">
-        <v>3.872589162021345</v>
+        <v>3.863458872952941</v>
       </c>
       <c r="N9" t="n">
-        <v>23.39056642886344</v>
+        <v>23.32546618305559</v>
       </c>
       <c r="O9" t="n">
-        <v>4.836379475275224</v>
+        <v>4.829644519325992</v>
       </c>
       <c r="P9" t="n">
-        <v>360.1925928293135</v>
+        <v>360.1903172368515</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39802,28 +39912,28 @@
         <v>0.1177</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07710946165289335</v>
+        <v>0.08037375536363248</v>
       </c>
       <c r="J10" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="K10" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="L10" t="n">
-        <v>0.009231828805662756</v>
+        <v>0.01005726975778065</v>
       </c>
       <c r="M10" t="n">
-        <v>4.891558272298899</v>
+        <v>4.895764484563735</v>
       </c>
       <c r="N10" t="n">
-        <v>34.75712745251558</v>
+        <v>34.75098914545942</v>
       </c>
       <c r="O10" t="n">
-        <v>5.895517572912117</v>
+        <v>5.894996958901626</v>
       </c>
       <c r="P10" t="n">
-        <v>354.2669782011315</v>
+        <v>354.2328876212923</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -39880,28 +39990,28 @@
         <v>0.1328</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1539842776268479</v>
+        <v>0.1570217459084224</v>
       </c>
       <c r="J11" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="K11" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03481594032831759</v>
+        <v>0.03629162265345132</v>
       </c>
       <c r="M11" t="n">
-        <v>4.854632201947126</v>
+        <v>4.855397215814953</v>
       </c>
       <c r="N11" t="n">
-        <v>35.80379005383397</v>
+        <v>35.78224040654508</v>
       </c>
       <c r="O11" t="n">
-        <v>5.98362683109784</v>
+        <v>5.981825842211145</v>
       </c>
       <c r="P11" t="n">
-        <v>343.3803079253701</v>
+        <v>343.3485846344709</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -39958,28 +40068,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1920869652293628</v>
+        <v>0.1930006204699389</v>
       </c>
       <c r="J12" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="K12" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06142657885451741</v>
+        <v>0.06232535953576546</v>
       </c>
       <c r="M12" t="n">
-        <v>4.445599092574354</v>
+        <v>4.436608994801744</v>
       </c>
       <c r="N12" t="n">
-        <v>30.70802916021028</v>
+        <v>30.62763524368397</v>
       </c>
       <c r="O12" t="n">
-        <v>5.541482577813476</v>
+        <v>5.534223996522364</v>
       </c>
       <c r="P12" t="n">
-        <v>341.7788293450194</v>
+        <v>341.7692881389929</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -40017,7 +40127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M699"/>
+  <dimension ref="A1:M701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86849,6 +86959,140 @@
         </is>
       </c>
     </row>
+    <row r="700">
+      <c r="A700" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:00:08+00:00</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>-37.145384424843364,175.87939845770526</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>-37.14609843046891,175.879475943788</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>-37.146802216461,175.87964946188396</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>-37.14751043416437,175.8797655244161</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>-37.148217326881124,175.87988047406236</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>-37.148924453611286,175.8800335286595</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>-37.14962555874807,175.88020980287462</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>-37.150325006251464,175.8803302389793</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>-37.1510136616941,175.88056889101804</t>
+        </is>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>-37.15172419996585,175.88074373884686</t>
+        </is>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>-37.15240625527363,175.8810313264019</t>
+        </is>
+      </c>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>-37.145385575414956,175.8793876389177</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>-37.146099154028846,175.87946914015762</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>-37.14680337891729,175.87963853136358</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>-37.14751244563896,175.87974452100343</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>-37.14821860492652,175.87986322000066</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>-37.148925887271844,175.8800107576177</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>-37.149626481063095,175.8802021249633</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>-37.15032819706937,175.88031558098012</t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>-37.15101420238151,175.8805668626097</t>
+        </is>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>-37.151722889191305,175.88074805189265</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>-37.15240711898093,175.8810287284727</t>
+        </is>
+      </c>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0192/nzd0192.xlsx
+++ b/data/nzd0192/nzd0192.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M701"/>
+  <dimension ref="A1:M702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31991,6 +31991,51 @@
         <v>348.32</v>
       </c>
       <c r="M701" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:16+00:00</t>
+        </is>
+      </c>
+      <c r="B702" t="n">
+        <v>340.02</v>
+      </c>
+      <c r="C702" t="n">
+        <v>335.58</v>
+      </c>
+      <c r="D702" t="n">
+        <v>342.02</v>
+      </c>
+      <c r="E702" t="n">
+        <v>342.75</v>
+      </c>
+      <c r="F702" t="n">
+        <v>345.27</v>
+      </c>
+      <c r="G702" t="n">
+        <v>355.24</v>
+      </c>
+      <c r="H702" t="n">
+        <v>370.05</v>
+      </c>
+      <c r="I702" t="n">
+        <v>364.52</v>
+      </c>
+      <c r="J702" t="n">
+        <v>364.69</v>
+      </c>
+      <c r="K702" t="n">
+        <v>354.9</v>
+      </c>
+      <c r="L702" t="n">
+        <v>349.51</v>
+      </c>
+      <c r="M702" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32007,7 +32052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B711"/>
+  <dimension ref="A1:B712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39120,6 +39165,16 @@
       </c>
       <c r="B711" t="n">
         <v>-0.41</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -39288,28 +39343,28 @@
         <v>0.1845</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1637785670278611</v>
+        <v>0.1629706833920039</v>
       </c>
       <c r="J2" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="K2" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05369974446026315</v>
+        <v>0.05333550082596661</v>
       </c>
       <c r="M2" t="n">
-        <v>4.068764805213444</v>
+        <v>4.066889605213004</v>
       </c>
       <c r="N2" t="n">
-        <v>25.83327992903433</v>
+        <v>25.80779138733855</v>
       </c>
       <c r="O2" t="n">
-        <v>5.082644973735066</v>
+        <v>5.080136945726813</v>
       </c>
       <c r="P2" t="n">
-        <v>338.5209258801421</v>
+        <v>338.5293960001871</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -39366,28 +39421,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3430123185983322</v>
+        <v>0.3407500499242764</v>
       </c>
       <c r="J3" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="K3" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1274667898291936</v>
+        <v>0.1261248873561331</v>
       </c>
       <c r="M3" t="n">
-        <v>5.491959737255213</v>
+        <v>5.495234995571377</v>
       </c>
       <c r="N3" t="n">
-        <v>44.01624896053599</v>
+        <v>44.0425634518631</v>
       </c>
       <c r="O3" t="n">
-        <v>6.63447427913742</v>
+        <v>6.636457146088047</v>
       </c>
       <c r="P3" t="n">
-        <v>334.4346623687329</v>
+        <v>334.4583807439951</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39444,28 +39499,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2492450530098429</v>
+        <v>0.2480887495776853</v>
       </c>
       <c r="J4" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="K4" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09800242499076695</v>
+        <v>0.0973936143356855</v>
       </c>
       <c r="M4" t="n">
-        <v>4.625980895767838</v>
+        <v>4.624824469369216</v>
       </c>
       <c r="N4" t="n">
-        <v>31.24858238804958</v>
+        <v>31.22728390172945</v>
       </c>
       <c r="O4" t="n">
-        <v>5.590043147243998</v>
+        <v>5.588137784783894</v>
       </c>
       <c r="P4" t="n">
-        <v>339.4743206585111</v>
+        <v>339.4864437272851</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39522,28 +39577,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.306000975078249</v>
+        <v>0.3041886506154627</v>
       </c>
       <c r="J5" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="K5" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1339855438522073</v>
+        <v>0.1327752280308468</v>
       </c>
       <c r="M5" t="n">
-        <v>4.564731697011801</v>
+        <v>4.565910335048149</v>
       </c>
       <c r="N5" t="n">
-        <v>33.07664839368073</v>
+        <v>33.08664899926196</v>
       </c>
       <c r="O5" t="n">
-        <v>5.751230163511171</v>
+        <v>5.752099529672792</v>
       </c>
       <c r="P5" t="n">
-        <v>341.0025627171497</v>
+        <v>341.0215637280367</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39600,28 +39655,28 @@
         <v>0.1235</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2880852017671739</v>
+        <v>0.2859229651287759</v>
       </c>
       <c r="J6" t="n">
+        <v>701</v>
+      </c>
+      <c r="K6" t="n">
         <v>700</v>
       </c>
-      <c r="K6" t="n">
-        <v>699</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1103166182721725</v>
+        <v>0.1089362382246333</v>
       </c>
       <c r="M6" t="n">
-        <v>5.050496450071545</v>
+        <v>5.055245483830522</v>
       </c>
       <c r="N6" t="n">
-        <v>36.40314899857991</v>
+        <v>36.43196903743202</v>
       </c>
       <c r="O6" t="n">
-        <v>6.033502216671501</v>
+        <v>6.035890078309248</v>
       </c>
       <c r="P6" t="n">
-        <v>345.1957743409239</v>
+        <v>345.2185222293073</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39678,28 +39733,28 @@
         <v>0.1494</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1680974869303976</v>
+        <v>0.1668964504584095</v>
       </c>
       <c r="J7" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="K7" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05972109167030082</v>
+        <v>0.05903770624493276</v>
       </c>
       <c r="M7" t="n">
-        <v>4.094580089678516</v>
+        <v>4.094906823930102</v>
       </c>
       <c r="N7" t="n">
-        <v>24.31420510304478</v>
+        <v>24.30463470611097</v>
       </c>
       <c r="O7" t="n">
-        <v>4.930943632109861</v>
+        <v>4.929973093852641</v>
       </c>
       <c r="P7" t="n">
-        <v>355.0053508601869</v>
+        <v>355.0179429249902</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39756,28 +39811,28 @@
         <v>0.1153</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1512280256635285</v>
+        <v>0.1520671551042823</v>
       </c>
       <c r="J8" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="K8" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0347284769425803</v>
+        <v>0.03519586797821861</v>
       </c>
       <c r="M8" t="n">
-        <v>4.64562112340172</v>
+        <v>4.642336810713367</v>
       </c>
       <c r="N8" t="n">
-        <v>34.74057475229837</v>
+        <v>34.70327564598291</v>
       </c>
       <c r="O8" t="n">
-        <v>5.894113567984449</v>
+        <v>5.890948620212445</v>
       </c>
       <c r="P8" t="n">
-        <v>363.1098090410278</v>
+        <v>363.1010113295987</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -39834,28 +39889,28 @@
         <v>0.1881</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09836584439830896</v>
+        <v>0.0988587344020964</v>
       </c>
       <c r="J9" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="K9" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02216823594093331</v>
+        <v>0.02245079170714726</v>
       </c>
       <c r="M9" t="n">
-        <v>3.863458872952941</v>
+        <v>3.860398532852839</v>
       </c>
       <c r="N9" t="n">
-        <v>23.32546618305559</v>
+        <v>23.29642137110439</v>
       </c>
       <c r="O9" t="n">
-        <v>4.829644519325992</v>
+        <v>4.826636652069886</v>
       </c>
       <c r="P9" t="n">
-        <v>360.1903172368515</v>
+        <v>360.1851496145408</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39912,28 +39967,28 @@
         <v>0.1177</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08037375536363248</v>
+        <v>0.08275220956209724</v>
       </c>
       <c r="J10" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="K10" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01005726975778065</v>
+        <v>0.01065809662815798</v>
       </c>
       <c r="M10" t="n">
-        <v>4.895764484563735</v>
+        <v>4.901933178008941</v>
       </c>
       <c r="N10" t="n">
-        <v>34.75098914545942</v>
+        <v>34.799908386557</v>
       </c>
       <c r="O10" t="n">
-        <v>5.894996958901626</v>
+        <v>5.899144716529422</v>
       </c>
       <c r="P10" t="n">
-        <v>354.2328876212923</v>
+        <v>354.2079511184489</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -39990,28 +40045,28 @@
         <v>0.1328</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1570217459084224</v>
+        <v>0.1591341859921409</v>
       </c>
       <c r="J11" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="K11" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03629162265345132</v>
+        <v>0.0372727588466194</v>
       </c>
       <c r="M11" t="n">
-        <v>4.855397215814953</v>
+        <v>4.858552228411098</v>
       </c>
       <c r="N11" t="n">
-        <v>35.78224040654508</v>
+        <v>35.80888907910851</v>
       </c>
       <c r="O11" t="n">
-        <v>5.981825842211145</v>
+        <v>5.984052897418982</v>
       </c>
       <c r="P11" t="n">
-        <v>343.3485846344709</v>
+        <v>343.3264371118539</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -40068,28 +40123,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1930006204699389</v>
+        <v>0.1937533137834513</v>
       </c>
       <c r="J12" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="K12" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06232535953576546</v>
+        <v>0.06294781691587081</v>
       </c>
       <c r="M12" t="n">
-        <v>4.436608994801744</v>
+        <v>4.43330357727976</v>
       </c>
       <c r="N12" t="n">
-        <v>30.62763524368397</v>
+        <v>30.59380783791789</v>
       </c>
       <c r="O12" t="n">
-        <v>5.534223996522364</v>
+        <v>5.531166950826732</v>
       </c>
       <c r="P12" t="n">
-        <v>341.7692881389929</v>
+        <v>341.7613966525961</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -40127,7 +40182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M701"/>
+  <dimension ref="A1:M702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87093,6 +87148,73 @@
         </is>
       </c>
     </row>
+    <row r="702">
+      <c r="A702" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:16+00:00</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>-37.145383831764846,175.87940403439973</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>-37.14610062487078,175.8794553098265</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>-37.14680450578726,175.8796279354506</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>-37.14751319459132,175.87973670058346</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>-37.148220165134425,175.87984215659964</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>-37.148926141516604,175.88000671940327</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>-37.149623861152456,175.88022393468182</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>-37.15032339902399,175.88033762226726</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>-37.1510063766394,175.88059622114886</t>
+        </is>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>-37.151716750928,175.88076824956852</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>-37.152403007733696,175.8810410946152</t>
+        </is>
+      </c>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0192/nzd0192.xlsx
+++ b/data/nzd0192/nzd0192.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M702"/>
+  <dimension ref="A1:M705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32036,6 +32036,141 @@
         <v>349.51</v>
       </c>
       <c r="M702" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-02 22:00:02+00:00</t>
+        </is>
+      </c>
+      <c r="B703" t="n">
+        <v>340.02</v>
+      </c>
+      <c r="C703" t="n">
+        <v>335.22</v>
+      </c>
+      <c r="D703" t="n">
+        <v>340.69</v>
+      </c>
+      <c r="E703" t="n">
+        <v>341.56</v>
+      </c>
+      <c r="F703" t="n">
+        <v>343.9</v>
+      </c>
+      <c r="G703" t="n">
+        <v>354.56</v>
+      </c>
+      <c r="H703" t="n">
+        <v>369.08</v>
+      </c>
+      <c r="I703" t="n">
+        <v>364.27</v>
+      </c>
+      <c r="J703" t="n">
+        <v>364.43</v>
+      </c>
+      <c r="K703" t="n">
+        <v>355.21</v>
+      </c>
+      <c r="L703" t="n">
+        <v>349.31</v>
+      </c>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B704" t="n">
+        <v>340.11</v>
+      </c>
+      <c r="C704" t="n">
+        <v>335.51</v>
+      </c>
+      <c r="D704" t="n">
+        <v>339.85</v>
+      </c>
+      <c r="E704" t="n">
+        <v>341.64</v>
+      </c>
+      <c r="F704" t="n">
+        <v>343.69</v>
+      </c>
+      <c r="G704" t="n">
+        <v>354.97</v>
+      </c>
+      <c r="H704" t="n">
+        <v>369.69</v>
+      </c>
+      <c r="I704" t="n">
+        <v>364.59</v>
+      </c>
+      <c r="J704" t="n">
+        <v>364.97</v>
+      </c>
+      <c r="K704" t="n">
+        <v>355.37</v>
+      </c>
+      <c r="L704" t="n">
+        <v>349.67</v>
+      </c>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="B705" t="n">
+        <v>340.8</v>
+      </c>
+      <c r="C705" t="n">
+        <v>336.67</v>
+      </c>
+      <c r="D705" t="n">
+        <v>340.56</v>
+      </c>
+      <c r="E705" t="n">
+        <v>341.9</v>
+      </c>
+      <c r="F705" t="n">
+        <v>344.68</v>
+      </c>
+      <c r="G705" t="n">
+        <v>355.31</v>
+      </c>
+      <c r="H705" t="n">
+        <v>370.44</v>
+      </c>
+      <c r="I705" t="n">
+        <v>364.97</v>
+      </c>
+      <c r="J705" t="n">
+        <v>365.4</v>
+      </c>
+      <c r="K705" t="n">
+        <v>356.51</v>
+      </c>
+      <c r="L705" t="n">
+        <v>350.22</v>
+      </c>
+      <c r="M705" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32052,7 +32187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B712"/>
+  <dimension ref="A1:B715"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39175,6 +39310,36 @@
       </c>
       <c r="B712" t="n">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-01-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>
@@ -39343,28 +39508,28 @@
         <v>0.1845</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1629706833920039</v>
+        <v>0.1608219164301904</v>
       </c>
       <c r="J2" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="K2" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05333550082596661</v>
+        <v>0.0524216042499438</v>
       </c>
       <c r="M2" t="n">
-        <v>4.066889605213004</v>
+        <v>4.059930367915535</v>
       </c>
       <c r="N2" t="n">
-        <v>25.80779138733855</v>
+        <v>25.72532491768684</v>
       </c>
       <c r="O2" t="n">
-        <v>5.080136945726813</v>
+        <v>5.07201389170878</v>
       </c>
       <c r="P2" t="n">
-        <v>338.5293960001871</v>
+        <v>338.551958246715</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -39421,28 +39586,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3407500499242764</v>
+        <v>0.3342368128048591</v>
       </c>
       <c r="J3" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="K3" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1261248873561331</v>
+        <v>0.1223271506822652</v>
       </c>
       <c r="M3" t="n">
-        <v>5.495234995571377</v>
+        <v>5.503850401923743</v>
       </c>
       <c r="N3" t="n">
-        <v>44.0425634518631</v>
+        <v>44.1046038876752</v>
       </c>
       <c r="O3" t="n">
-        <v>6.636457146088047</v>
+        <v>6.641129714715351</v>
       </c>
       <c r="P3" t="n">
-        <v>334.4583807439951</v>
+        <v>334.5267712528014</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39499,28 +39664,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2480887495776853</v>
+        <v>0.2432674529525716</v>
       </c>
       <c r="J4" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="K4" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0973936143356855</v>
+        <v>0.09442286017479562</v>
       </c>
       <c r="M4" t="n">
-        <v>4.624824469369216</v>
+        <v>4.627731241785682</v>
       </c>
       <c r="N4" t="n">
-        <v>31.22728390172945</v>
+        <v>31.23071123655311</v>
       </c>
       <c r="O4" t="n">
-        <v>5.588137784783894</v>
+        <v>5.58844443799463</v>
       </c>
       <c r="P4" t="n">
-        <v>339.4864437272851</v>
+        <v>339.5370705032879</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39577,28 +39742,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3041886506154627</v>
+        <v>0.2979363622045713</v>
       </c>
       <c r="J5" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="K5" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1327752280308468</v>
+        <v>0.1283388923876414</v>
       </c>
       <c r="M5" t="n">
-        <v>4.565910335048149</v>
+        <v>4.573959583438181</v>
       </c>
       <c r="N5" t="n">
-        <v>33.08664899926196</v>
+        <v>33.17431491127</v>
       </c>
       <c r="O5" t="n">
-        <v>5.752099529672792</v>
+        <v>5.759714828988497</v>
       </c>
       <c r="P5" t="n">
-        <v>341.0215637280367</v>
+        <v>341.087215464303</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39655,28 +39820,28 @@
         <v>0.1235</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2859229651287759</v>
+        <v>0.278515321263178</v>
       </c>
       <c r="J6" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="K6" t="n">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1089362382246333</v>
+        <v>0.104001896559618</v>
       </c>
       <c r="M6" t="n">
-        <v>5.055245483830522</v>
+        <v>5.074736853255202</v>
       </c>
       <c r="N6" t="n">
-        <v>36.43196903743202</v>
+        <v>36.59586475298564</v>
       </c>
       <c r="O6" t="n">
-        <v>6.035890078309248</v>
+        <v>6.049451607624087</v>
       </c>
       <c r="P6" t="n">
-        <v>345.2185222293073</v>
+        <v>345.2965736109457</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39733,28 +39898,28 @@
         <v>0.1494</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1668964504584095</v>
+        <v>0.1630875694298707</v>
       </c>
       <c r="J7" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="K7" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05903770624493276</v>
+        <v>0.05683720078669896</v>
       </c>
       <c r="M7" t="n">
-        <v>4.094906823930102</v>
+        <v>4.09687008115784</v>
       </c>
       <c r="N7" t="n">
-        <v>24.30463470611097</v>
+        <v>24.28629477205826</v>
       </c>
       <c r="O7" t="n">
-        <v>4.929973093852641</v>
+        <v>4.928112698798421</v>
       </c>
       <c r="P7" t="n">
-        <v>355.0179429249902</v>
+        <v>355.057936994159</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39811,28 +39976,28 @@
         <v>0.1153</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1520671551042823</v>
+        <v>0.15427781379603</v>
       </c>
       <c r="J8" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="K8" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03519586797821861</v>
+        <v>0.03648706230791565</v>
       </c>
       <c r="M8" t="n">
-        <v>4.642336810713367</v>
+        <v>4.631345918200001</v>
       </c>
       <c r="N8" t="n">
-        <v>34.70327564598291</v>
+        <v>34.58526947553591</v>
       </c>
       <c r="O8" t="n">
-        <v>5.890948620212445</v>
+        <v>5.88092420249878</v>
       </c>
       <c r="P8" t="n">
-        <v>363.1010113295987</v>
+        <v>363.0777964308115</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -39889,28 +40054,28 @@
         <v>0.1881</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0988587344020964</v>
+        <v>0.1003920044595356</v>
       </c>
       <c r="J9" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="K9" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02245079170714726</v>
+        <v>0.02333516962396054</v>
       </c>
       <c r="M9" t="n">
-        <v>3.860398532852839</v>
+        <v>3.851561019052181</v>
       </c>
       <c r="N9" t="n">
-        <v>23.29642137110439</v>
+        <v>23.21124296880994</v>
       </c>
       <c r="O9" t="n">
-        <v>4.826636652069886</v>
+        <v>4.817804787328971</v>
       </c>
       <c r="P9" t="n">
-        <v>360.1851496145408</v>
+        <v>360.1690485309426</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39967,28 +40132,28 @@
         <v>0.1177</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08275220956209724</v>
+        <v>0.08998942008246473</v>
       </c>
       <c r="J10" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="K10" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01065809662815798</v>
+        <v>0.01258620239639374</v>
       </c>
       <c r="M10" t="n">
-        <v>4.901933178008941</v>
+        <v>4.920921668010139</v>
       </c>
       <c r="N10" t="n">
-        <v>34.799908386557</v>
+        <v>34.95851258681232</v>
       </c>
       <c r="O10" t="n">
-        <v>5.899144716529422</v>
+        <v>5.912572417045928</v>
       </c>
       <c r="P10" t="n">
-        <v>354.2079511184489</v>
+        <v>354.1319553664725</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -40045,28 +40210,28 @@
         <v>0.1328</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1591341859921409</v>
+        <v>0.1660507285947254</v>
       </c>
       <c r="J11" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="K11" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0372727588466194</v>
+        <v>0.04050810187873244</v>
       </c>
       <c r="M11" t="n">
-        <v>4.858552228411098</v>
+        <v>4.870730553204888</v>
       </c>
       <c r="N11" t="n">
-        <v>35.80888907910851</v>
+        <v>35.93739134546263</v>
       </c>
       <c r="O11" t="n">
-        <v>5.984052897418982</v>
+        <v>5.994780341719172</v>
       </c>
       <c r="P11" t="n">
-        <v>343.3264371118539</v>
+        <v>343.2538084698982</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -40123,28 +40288,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1937533137834513</v>
+        <v>0.1961616484112727</v>
       </c>
       <c r="J12" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="K12" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06294781691587081</v>
+        <v>0.06491910072014362</v>
       </c>
       <c r="M12" t="n">
-        <v>4.43330357727976</v>
+        <v>4.424006442013578</v>
       </c>
       <c r="N12" t="n">
-        <v>30.59380783791789</v>
+        <v>30.49793643537637</v>
       </c>
       <c r="O12" t="n">
-        <v>5.531166950826732</v>
+        <v>5.522493679070748</v>
       </c>
       <c r="P12" t="n">
-        <v>341.7613966525961</v>
+        <v>341.736106710663</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -40182,7 +40347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M702"/>
+  <dimension ref="A1:M705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87215,6 +87380,207 @@
         </is>
       </c>
     </row>
+    <row r="703">
+      <c r="A703" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-02 22:00:02+00:00</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>-37.145383831764846,175.87940403439973</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>-37.14610105188912,175.87945129456898</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>-37.146806083403625,175.87961310117183</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>-37.14751446780918,175.87972340586913</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>-37.14822130209209,175.87982680720563</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>-37.14892662175635,175.8799990916648</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>-37.1496251577414,175.88021314109687</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>-37.1503239899165,175.8803349078232</t>
+        </is>
+      </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>-37.15100711652805,175.8805934454327</t>
+        </is>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>-37.15171575985393,175.88077151065124</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>-37.1524036986997,175.88103901627204</t>
+        </is>
+      </c>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>-37.14538372501067,175.8794050382047</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>-37.14610070790215,175.87945452908198</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>-37.14680707979196,175.87960373215324</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>-37.14751438221473,175.87972429963145</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>-37.14822147637011,175.87982445437873</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>-37.14892633220009,175.88000369074243</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>-37.14962434236084,175.88021992881528</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>-37.150323233574085,175.8803383823116</t>
+        </is>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>-37.15100557983618,175.88059921038158</t>
+        </is>
+      </c>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>-37.15171524833179,175.88077319379073</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>-37.152402454960864,175.88104275728972</t>
+        </is>
+      </c>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>-37.14538290656184,175.8794127340429</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>-37.146099331953366,175.8794674671337</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>-37.146806237606626,175.87961165120467</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>-37.1475141040328,175.879727204359</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>-37.14822065477336,175.87983554627675</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>-37.14892609208014,175.88000750461165</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>-37.149623339843245,175.8802282743705</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>-37.150322335417336,175.88034250826647</t>
+        </is>
+      </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>-37.151004356173935,175.88060380098884</t>
+        </is>
+      </c>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>-37.151711603735905,175.8807851861586</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>-37.15240055480409,175.88104847273317</t>
+        </is>
+      </c>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0192/nzd0192.xlsx
+++ b/data/nzd0192/nzd0192.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M705"/>
+  <dimension ref="A1:M706"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32173,6 +32173,51 @@
       <c r="M705" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-03 21:59:54+00:00</t>
+        </is>
+      </c>
+      <c r="B706" t="n">
+        <v>341</v>
+      </c>
+      <c r="C706" t="n">
+        <v>336.84</v>
+      </c>
+      <c r="D706" t="n">
+        <v>339.58</v>
+      </c>
+      <c r="E706" t="n">
+        <v>341.69</v>
+      </c>
+      <c r="F706" t="n">
+        <v>344.88</v>
+      </c>
+      <c r="G706" t="n">
+        <v>355.77</v>
+      </c>
+      <c r="H706" t="n">
+        <v>369.9</v>
+      </c>
+      <c r="I706" t="n">
+        <v>365.32</v>
+      </c>
+      <c r="J706" t="n">
+        <v>365.94</v>
+      </c>
+      <c r="K706" t="n">
+        <v>357.04</v>
+      </c>
+      <c r="L706" t="n">
+        <v>350.79</v>
+      </c>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -32187,7 +32232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B715"/>
+  <dimension ref="A1:B716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39340,6 +39385,16 @@
       </c>
       <c r="B715" t="n">
         <v>0.19</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-02-03 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>0.6899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -39508,28 +39563,28 @@
         <v>0.1845</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1608219164301904</v>
+        <v>0.1603057503909644</v>
       </c>
       <c r="J2" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K2" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0524216042499438</v>
+        <v>0.05224877005700723</v>
       </c>
       <c r="M2" t="n">
-        <v>4.059930367915535</v>
+        <v>4.056641515787181</v>
       </c>
       <c r="N2" t="n">
-        <v>25.72532491768684</v>
+        <v>25.6935239278018</v>
       </c>
       <c r="O2" t="n">
-        <v>5.07201389170878</v>
+        <v>5.068877975232961</v>
       </c>
       <c r="P2" t="n">
-        <v>338.551958246715</v>
+        <v>338.5573956453932</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -39586,28 +39641,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3342368128048591</v>
+        <v>0.3323797948703888</v>
       </c>
       <c r="J3" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K3" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1223271506822652</v>
+        <v>0.1213222679977864</v>
       </c>
       <c r="M3" t="n">
-        <v>5.503850401923743</v>
+        <v>5.505195434591568</v>
       </c>
       <c r="N3" t="n">
-        <v>44.1046038876752</v>
+        <v>44.10273429734841</v>
       </c>
       <c r="O3" t="n">
-        <v>6.641129714715351</v>
+        <v>6.640988954767837</v>
       </c>
       <c r="P3" t="n">
-        <v>334.5267712528014</v>
+        <v>334.5463334597172</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39664,28 +39719,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2432674529525716</v>
+        <v>0.2414498683594496</v>
       </c>
       <c r="J4" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K4" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09442286017479562</v>
+        <v>0.09325497406962413</v>
       </c>
       <c r="M4" t="n">
-        <v>4.627731241785682</v>
+        <v>4.62966600178276</v>
       </c>
       <c r="N4" t="n">
-        <v>31.23071123655311</v>
+        <v>31.24455237148915</v>
       </c>
       <c r="O4" t="n">
-        <v>5.58844443799463</v>
+        <v>5.589682671806079</v>
       </c>
       <c r="P4" t="n">
-        <v>339.5370705032879</v>
+        <v>339.5562173113168</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39742,28 +39797,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2979363622045713</v>
+        <v>0.2958654317053214</v>
       </c>
       <c r="J5" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K5" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1283388923876414</v>
+        <v>0.1268806438707863</v>
       </c>
       <c r="M5" t="n">
-        <v>4.573959583438181</v>
+        <v>4.57665089211729</v>
       </c>
       <c r="N5" t="n">
-        <v>33.17431491127</v>
+        <v>33.20273654531433</v>
       </c>
       <c r="O5" t="n">
-        <v>5.759714828988497</v>
+        <v>5.762181578648344</v>
       </c>
       <c r="P5" t="n">
-        <v>341.087215464303</v>
+        <v>341.1090310699483</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39820,28 +39875,28 @@
         <v>0.1235</v>
       </c>
       <c r="I6" t="n">
-        <v>0.278515321263178</v>
+        <v>0.2762936423147799</v>
       </c>
       <c r="J6" t="n">
+        <v>705</v>
+      </c>
+      <c r="K6" t="n">
         <v>704</v>
       </c>
-      <c r="K6" t="n">
-        <v>703</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.104001896559618</v>
+        <v>0.1025901930012463</v>
       </c>
       <c r="M6" t="n">
-        <v>5.074736853255202</v>
+        <v>5.079813850440851</v>
       </c>
       <c r="N6" t="n">
-        <v>36.59586475298564</v>
+        <v>36.63013637236955</v>
       </c>
       <c r="O6" t="n">
-        <v>6.049451607624087</v>
+        <v>6.052283566751441</v>
       </c>
       <c r="P6" t="n">
-        <v>345.2965736109457</v>
+        <v>345.320057576435</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39898,28 +39953,28 @@
         <v>0.1494</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1630875694298707</v>
+        <v>0.1620639986809352</v>
       </c>
       <c r="J7" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K7" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05683720078669896</v>
+        <v>0.05629155679098685</v>
       </c>
       <c r="M7" t="n">
-        <v>4.09687008115784</v>
+        <v>4.096231945848004</v>
       </c>
       <c r="N7" t="n">
-        <v>24.28629477205826</v>
+        <v>24.27028445833481</v>
       </c>
       <c r="O7" t="n">
-        <v>4.928112698798421</v>
+        <v>4.926488045081893</v>
       </c>
       <c r="P7" t="n">
-        <v>355.057936994159</v>
+        <v>355.0687194978776</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39976,28 +40031,28 @@
         <v>0.1153</v>
       </c>
       <c r="I8" t="n">
-        <v>0.15427781379603</v>
+        <v>0.1550493787688109</v>
       </c>
       <c r="J8" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K8" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03648706230791565</v>
+        <v>0.03693977612553512</v>
       </c>
       <c r="M8" t="n">
-        <v>4.631345918200001</v>
+        <v>4.627847419778509</v>
       </c>
       <c r="N8" t="n">
-        <v>34.58526947553591</v>
+        <v>34.54668920965306</v>
       </c>
       <c r="O8" t="n">
-        <v>5.88092420249878</v>
+        <v>5.877643167941812</v>
       </c>
       <c r="P8" t="n">
-        <v>363.0777964308115</v>
+        <v>363.0696686075061</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -40054,28 +40109,28 @@
         <v>0.1881</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1003920044595356</v>
+        <v>0.1010948342716379</v>
       </c>
       <c r="J9" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K9" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02333516962396054</v>
+        <v>0.0237189349165613</v>
       </c>
       <c r="M9" t="n">
-        <v>3.851561019052181</v>
+        <v>3.849566625488043</v>
       </c>
       <c r="N9" t="n">
-        <v>23.21124296880994</v>
+        <v>23.18701255124289</v>
       </c>
       <c r="O9" t="n">
-        <v>4.817804787328971</v>
+        <v>4.81528945664151</v>
       </c>
       <c r="P9" t="n">
-        <v>360.1690485309426</v>
+        <v>360.1616447778846</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -40132,28 +40187,28 @@
         <v>0.1177</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08998942008246473</v>
+        <v>0.09265612284966239</v>
       </c>
       <c r="J10" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K10" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01258620239639374</v>
+        <v>0.01332716939163958</v>
       </c>
       <c r="M10" t="n">
-        <v>4.920921668010139</v>
+        <v>4.92854572002965</v>
       </c>
       <c r="N10" t="n">
-        <v>34.95851258681232</v>
+        <v>35.03407726933188</v>
       </c>
       <c r="O10" t="n">
-        <v>5.912572417045928</v>
+        <v>5.918959137325741</v>
       </c>
       <c r="P10" t="n">
-        <v>354.1319553664725</v>
+        <v>354.1038637738463</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -40210,28 +40265,28 @@
         <v>0.1328</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1660507285947254</v>
+        <v>0.1687057612768085</v>
       </c>
       <c r="J11" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K11" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04050810187873244</v>
+        <v>0.04174636292478673</v>
       </c>
       <c r="M11" t="n">
-        <v>4.870730553204888</v>
+        <v>4.876482903036825</v>
       </c>
       <c r="N11" t="n">
-        <v>35.93739134546263</v>
+        <v>36.01047456502649</v>
       </c>
       <c r="O11" t="n">
-        <v>5.994780341719172</v>
+        <v>6.000872816934757</v>
       </c>
       <c r="P11" t="n">
-        <v>343.2538084698982</v>
+        <v>343.2258398123365</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -40288,28 +40343,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1961616484112727</v>
+        <v>0.1972508669297263</v>
       </c>
       <c r="J12" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K12" t="n">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06491910072014362</v>
+        <v>0.06574444645301836</v>
       </c>
       <c r="M12" t="n">
-        <v>4.424006442013578</v>
+        <v>4.42203017410808</v>
       </c>
       <c r="N12" t="n">
-        <v>30.49793643537637</v>
+        <v>30.47555625015176</v>
       </c>
       <c r="O12" t="n">
-        <v>5.522493679070748</v>
+        <v>5.520467031887045</v>
       </c>
       <c r="P12" t="n">
-        <v>341.736106710663</v>
+        <v>341.7246326599073</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -40347,7 +40402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M705"/>
+  <dimension ref="A1:M706"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87581,6 +87636,73 @@
         </is>
       </c>
     </row>
+    <row r="706">
+      <c r="A706" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-03 21:59:54+00:00</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>-37.145382669330196,175.87941496472055</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>-37.14609913030557,175.87946936322749</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>-37.14680740005948,175.87960072068293</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>-37.147514328718216,175.87972485823292</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>-37.14822048879411,175.8798377870642</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>-37.148925767211765,175.88001266455228</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>-37.14962406165597,175.88022226557075</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>-37.150321508167586,175.88034630848796</t>
+        </is>
+      </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>-37.151002819481576,175.88060956593725</t>
+        </is>
+      </c>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>-37.15170990931812,175.8807907615573</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>-37.15239858555043,175.8810543960106</t>
+        </is>
+      </c>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0192/nzd0192.xlsx
+++ b/data/nzd0192/nzd0192.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M706"/>
+  <dimension ref="A1:M709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32218,6 +32218,141 @@
       <c r="M706" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-19 21:59:52+00:00</t>
+        </is>
+      </c>
+      <c r="B707" t="n">
+        <v>341.06</v>
+      </c>
+      <c r="C707" t="n">
+        <v>334.77</v>
+      </c>
+      <c r="D707" t="n">
+        <v>335.08</v>
+      </c>
+      <c r="E707" t="n">
+        <v>339.56</v>
+      </c>
+      <c r="F707" t="n">
+        <v>343.25</v>
+      </c>
+      <c r="G707" t="n">
+        <v>355.5</v>
+      </c>
+      <c r="H707" t="n">
+        <v>369.52</v>
+      </c>
+      <c r="I707" t="n">
+        <v>365.96</v>
+      </c>
+      <c r="J707" t="n">
+        <v>366.8</v>
+      </c>
+      <c r="K707" t="n">
+        <v>360.18</v>
+      </c>
+      <c r="L707" t="n">
+        <v>353.25</v>
+      </c>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>342.4</v>
+      </c>
+      <c r="C708" t="n">
+        <v>336.27</v>
+      </c>
+      <c r="D708" t="n">
+        <v>336.97</v>
+      </c>
+      <c r="E708" t="n">
+        <v>340.63</v>
+      </c>
+      <c r="F708" t="n">
+        <v>344.96</v>
+      </c>
+      <c r="G708" t="n">
+        <v>356.83</v>
+      </c>
+      <c r="H708" t="n">
+        <v>371.05</v>
+      </c>
+      <c r="I708" t="n">
+        <v>367.38</v>
+      </c>
+      <c r="J708" t="n">
+        <v>368.76</v>
+      </c>
+      <c r="K708" t="n">
+        <v>361.07</v>
+      </c>
+      <c r="L708" t="n">
+        <v>355.32</v>
+      </c>
+      <c r="M708" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 21:59:49+00:00</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>342.11</v>
+      </c>
+      <c r="C709" t="n">
+        <v>336.72</v>
+      </c>
+      <c r="D709" t="n">
+        <v>337.66</v>
+      </c>
+      <c r="E709" t="n">
+        <v>340.34</v>
+      </c>
+      <c r="F709" t="n">
+        <v>343.85</v>
+      </c>
+      <c r="G709" t="n">
+        <v>355.79</v>
+      </c>
+      <c r="H709" t="n">
+        <v>370.5</v>
+      </c>
+      <c r="I709" t="n">
+        <v>367.12</v>
+      </c>
+      <c r="J709" t="n">
+        <v>368.06</v>
+      </c>
+      <c r="K709" t="n">
+        <v>360.32</v>
+      </c>
+      <c r="L709" t="n">
+        <v>354.98</v>
+      </c>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -32232,7 +32367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B716"/>
+  <dimension ref="A1:B719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39395,6 +39530,36 @@
       </c>
       <c r="B716" t="n">
         <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-02-19 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B719" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -39563,28 +39728,28 @@
         <v>0.1845</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1603057503909644</v>
+        <v>0.1594904122778443</v>
       </c>
       <c r="J2" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="K2" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05224877005700723</v>
+        <v>0.05219859783682623</v>
       </c>
       <c r="M2" t="n">
-        <v>4.056641515787181</v>
+        <v>4.043313899942134</v>
       </c>
       <c r="N2" t="n">
-        <v>25.6935239278018</v>
+        <v>25.58995913071846</v>
       </c>
       <c r="O2" t="n">
-        <v>5.068877975232961</v>
+        <v>5.058651908435533</v>
       </c>
       <c r="P2" t="n">
-        <v>338.5573956453932</v>
+        <v>338.5660077348924</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -39641,28 +39806,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3323797948703888</v>
+        <v>0.3260735607403708</v>
       </c>
       <c r="J3" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="K3" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1213222679977864</v>
+        <v>0.1177141072280588</v>
       </c>
       <c r="M3" t="n">
-        <v>5.505195434591568</v>
+        <v>5.512869046029799</v>
       </c>
       <c r="N3" t="n">
-        <v>44.10273429734841</v>
+        <v>44.15235929524633</v>
       </c>
       <c r="O3" t="n">
-        <v>6.640988954767837</v>
+        <v>6.644724169989777</v>
       </c>
       <c r="P3" t="n">
-        <v>334.5463334597172</v>
+        <v>334.6129626218867</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39719,28 +39884,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2414498683594496</v>
+        <v>0.233508183427436</v>
       </c>
       <c r="J4" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="K4" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09325497406962413</v>
+        <v>0.08754244625845897</v>
       </c>
       <c r="M4" t="n">
-        <v>4.62966600178276</v>
+        <v>4.64702711901517</v>
       </c>
       <c r="N4" t="n">
-        <v>31.24455237148915</v>
+        <v>31.4876409294788</v>
       </c>
       <c r="O4" t="n">
-        <v>5.589682671806079</v>
+        <v>5.611384938629572</v>
       </c>
       <c r="P4" t="n">
-        <v>339.5562173113168</v>
+        <v>339.6401253652668</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39797,28 +39962,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2958654317053214</v>
+        <v>0.2884343384939473</v>
       </c>
       <c r="J5" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="K5" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1268806438707863</v>
+        <v>0.121308829883067</v>
       </c>
       <c r="M5" t="n">
-        <v>4.57665089211729</v>
+        <v>4.59030752555635</v>
       </c>
       <c r="N5" t="n">
-        <v>33.20273654531433</v>
+        <v>33.38717662840645</v>
       </c>
       <c r="O5" t="n">
-        <v>5.762181578648344</v>
+        <v>5.778163776530262</v>
       </c>
       <c r="P5" t="n">
-        <v>341.1090310699483</v>
+        <v>341.1875514556394</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39875,28 +40040,28 @@
         <v>0.1235</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2762936423147799</v>
+        <v>0.2689596884418558</v>
       </c>
       <c r="J6" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="K6" t="n">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1025901930012463</v>
+        <v>0.0978115091809274</v>
       </c>
       <c r="M6" t="n">
-        <v>5.079813850440851</v>
+        <v>5.098474080147225</v>
       </c>
       <c r="N6" t="n">
-        <v>36.63013637236955</v>
+        <v>36.79042117711036</v>
       </c>
       <c r="O6" t="n">
-        <v>6.052283566751441</v>
+        <v>6.06551079276184</v>
       </c>
       <c r="P6" t="n">
-        <v>345.320057576435</v>
+        <v>345.3978181569139</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39953,28 +40118,28 @@
         <v>0.1494</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1620639986809352</v>
+        <v>0.1592400920765321</v>
       </c>
       <c r="J7" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="K7" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05629155679098685</v>
+        <v>0.054835059276515</v>
       </c>
       <c r="M7" t="n">
-        <v>4.096231945848004</v>
+        <v>4.092989907305794</v>
       </c>
       <c r="N7" t="n">
-        <v>24.27028445833481</v>
+        <v>24.21564536451796</v>
       </c>
       <c r="O7" t="n">
-        <v>4.926488045081893</v>
+        <v>4.920939479867433</v>
       </c>
       <c r="P7" t="n">
-        <v>355.0687194978776</v>
+        <v>355.0985593410024</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -40031,28 +40196,28 @@
         <v>0.1153</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1550493787688109</v>
+        <v>0.1577164912467607</v>
       </c>
       <c r="J8" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="K8" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03693977612553512</v>
+        <v>0.03847224805025484</v>
       </c>
       <c r="M8" t="n">
-        <v>4.627847419778509</v>
+        <v>4.618795914751535</v>
       </c>
       <c r="N8" t="n">
-        <v>34.54668920965306</v>
+        <v>34.44374725946957</v>
       </c>
       <c r="O8" t="n">
-        <v>5.877643167941812</v>
+        <v>5.868879557417205</v>
       </c>
       <c r="P8" t="n">
-        <v>363.0696686075061</v>
+        <v>363.0414828931261</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -40109,28 +40274,28 @@
         <v>0.1881</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1010948342716379</v>
+        <v>0.1044418042341779</v>
       </c>
       <c r="J9" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="K9" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0237189349165613</v>
+        <v>0.02543523644494006</v>
       </c>
       <c r="M9" t="n">
-        <v>3.849566625488043</v>
+        <v>3.849764065219815</v>
       </c>
       <c r="N9" t="n">
-        <v>23.18701255124289</v>
+        <v>23.15610862976864</v>
       </c>
       <c r="O9" t="n">
-        <v>4.81528945664151</v>
+        <v>4.812079449652576</v>
       </c>
       <c r="P9" t="n">
-        <v>360.1616447778846</v>
+        <v>360.1262741935713</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -40187,28 +40352,28 @@
         <v>0.1177</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09265612284966239</v>
+        <v>0.1021929725760601</v>
       </c>
       <c r="J10" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="K10" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01332716939163958</v>
+        <v>0.01607200813119636</v>
       </c>
       <c r="M10" t="n">
-        <v>4.92854572002965</v>
+        <v>4.959454252643008</v>
       </c>
       <c r="N10" t="n">
-        <v>35.03407726933188</v>
+        <v>35.42233270152654</v>
       </c>
       <c r="O10" t="n">
-        <v>5.918959137325741</v>
+        <v>5.951666380227183</v>
       </c>
       <c r="P10" t="n">
-        <v>354.1038637738463</v>
+        <v>354.0030861785815</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -40265,28 +40430,28 @@
         <v>0.1328</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1687057612768085</v>
+        <v>0.1795092171128366</v>
       </c>
       <c r="J11" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="K11" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04174636292478673</v>
+        <v>0.0465785802004447</v>
       </c>
       <c r="M11" t="n">
-        <v>4.876482903036825</v>
+        <v>4.907188742199764</v>
       </c>
       <c r="N11" t="n">
-        <v>36.01047456502649</v>
+        <v>36.54383196022166</v>
       </c>
       <c r="O11" t="n">
-        <v>6.000872816934757</v>
+        <v>6.045149457227808</v>
       </c>
       <c r="P11" t="n">
-        <v>343.2258398123365</v>
+        <v>343.11168235886</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -40343,28 +40508,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1972508669297263</v>
+        <v>0.2036164079499035</v>
       </c>
       <c r="J12" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="K12" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06574444645301836</v>
+        <v>0.06985108079723801</v>
       </c>
       <c r="M12" t="n">
-        <v>4.42203017410808</v>
+        <v>4.428163797419832</v>
       </c>
       <c r="N12" t="n">
-        <v>30.47555625015176</v>
+        <v>30.58769985638888</v>
       </c>
       <c r="O12" t="n">
-        <v>5.520467031887045</v>
+        <v>5.530614781051821</v>
       </c>
       <c r="P12" t="n">
-        <v>341.7246326599073</v>
+        <v>341.6573635197565</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -40402,7 +40567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M706"/>
+  <dimension ref="A1:M709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87703,6 +87868,207 @@
         </is>
       </c>
     </row>
+    <row r="707">
+      <c r="A707" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-19 21:59:52+00:00</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>-37.145382598160694,175.87941563392386</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>-37.14610158566184,175.879446275497</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>-37.14681273784044,175.87955052950647</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>-37.14751660766778,175.87970106181018</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>-37.14822184152387,175.8798195246462</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>-37.1489259578954,175.88000963589147</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>-37.14962456959809,175.88021803715606</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>-37.15031999548199,175.88035325746418</t>
+        </is>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>-37.15100037215613,175.8806187471509</t>
+        </is>
+      </c>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>-37.15169987068682,175.8808237931592</t>
+        </is>
+      </c>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>-37.15239008666292,175.8810799596253</t>
+        </is>
+      </c>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>-37.14538100870754,175.87943057946396</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>-37.14609980641862,175.87946300573665</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>-37.146810495975004,175.8795716098016</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>-37.14751546284394,175.8797130158819</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>-37.14822042240238,175.87983868337915</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>-37.1489250186012,175.88002455485008</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>-37.14962252446185,175.88023506208853</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>-37.15031663920946,175.88036867550406</t>
+        </is>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>-37.150994794528174,175.88063967177496</t>
+        </is>
+      </c>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>-37.15169702534067,175.88083315561795</t>
+        </is>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>-37.15238293515591,175.88110147046714</t>
+        </is>
+      </c>
+      <c r="M708" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 21:59:49+00:00</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>-37.145381352693825,175.87942734498142</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>-37.1460992726452,175.87946802480838</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>-37.146809677515265,175.87957930578202</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>-37.14751577312342,175.87970977599335</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>-37.14822134358686,175.87982624700874</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>-37.148925753087056,175.88001288889754</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>-37.149623259641814,175.8802289420149</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>-37.150317253738365,175.88036585248278</t>
+        </is>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>-37.15099678653858,175.8806321986953</t>
+        </is>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>-37.15169942310433,175.88082526590557</t>
+        </is>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>-37.152384109799826,175.8810979372857</t>
+        </is>
+      </c>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0192/nzd0192.xlsx
+++ b/data/nzd0192/nzd0192.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M709"/>
+  <dimension ref="A1:M711"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32351,6 +32351,96 @@
         <v>354.98</v>
       </c>
       <c r="M709" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-08 21:59:26+00:00</t>
+        </is>
+      </c>
+      <c r="B710" t="n">
+        <v>341.89</v>
+      </c>
+      <c r="C710" t="n">
+        <v>336.65</v>
+      </c>
+      <c r="D710" t="n">
+        <v>337.41</v>
+      </c>
+      <c r="E710" t="n">
+        <v>339.8</v>
+      </c>
+      <c r="F710" t="n">
+        <v>344.31</v>
+      </c>
+      <c r="G710" t="n">
+        <v>355.2</v>
+      </c>
+      <c r="H710" t="n">
+        <v>370.14</v>
+      </c>
+      <c r="I710" t="n">
+        <v>366.01</v>
+      </c>
+      <c r="J710" t="n">
+        <v>368.76</v>
+      </c>
+      <c r="K710" t="n">
+        <v>361.54</v>
+      </c>
+      <c r="L710" t="n">
+        <v>355.02</v>
+      </c>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:59:37+00:00</t>
+        </is>
+      </c>
+      <c r="B711" t="n">
+        <v>342.21</v>
+      </c>
+      <c r="C711" t="n">
+        <v>338.18</v>
+      </c>
+      <c r="D711" t="n">
+        <v>338.57</v>
+      </c>
+      <c r="E711" t="n">
+        <v>340.54</v>
+      </c>
+      <c r="F711" t="n">
+        <v>345.56</v>
+      </c>
+      <c r="G711" t="n">
+        <v>355.67</v>
+      </c>
+      <c r="H711" t="n">
+        <v>370.68</v>
+      </c>
+      <c r="I711" t="n">
+        <v>366.17</v>
+      </c>
+      <c r="J711" t="n">
+        <v>368.6</v>
+      </c>
+      <c r="K711" t="n">
+        <v>360.77</v>
+      </c>
+      <c r="L711" t="n">
+        <v>355.17</v>
+      </c>
+      <c r="M711" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32367,7 +32457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B719"/>
+  <dimension ref="A1:B721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39560,6 +39650,26 @@
       </c>
       <c r="B719" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>
@@ -39728,28 +39838,28 @@
         <v>0.1845</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1594904122778443</v>
+        <v>0.1590508125134256</v>
       </c>
       <c r="J2" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="K2" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05219859783682623</v>
+        <v>0.05223360309977332</v>
       </c>
       <c r="M2" t="n">
-        <v>4.043313899942134</v>
+        <v>4.03397620957326</v>
       </c>
       <c r="N2" t="n">
-        <v>25.58995913071846</v>
+        <v>25.51964456876823</v>
       </c>
       <c r="O2" t="n">
-        <v>5.058651908435533</v>
+        <v>5.0516971968605</v>
       </c>
       <c r="P2" t="n">
-        <v>338.5660077348924</v>
+        <v>338.5706750563825</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -39806,28 +39916,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3260735607403708</v>
+        <v>0.3227420940350684</v>
       </c>
       <c r="J3" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="K3" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1177141072280588</v>
+        <v>0.1160116229044259</v>
       </c>
       <c r="M3" t="n">
-        <v>5.512869046029799</v>
+        <v>5.513539166757207</v>
       </c>
       <c r="N3" t="n">
-        <v>44.15235929524633</v>
+        <v>44.12734446104924</v>
       </c>
       <c r="O3" t="n">
-        <v>6.644724169989777</v>
+        <v>6.64284159536032</v>
       </c>
       <c r="P3" t="n">
-        <v>334.6129626218867</v>
+        <v>334.6483346441076</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39884,28 +39994,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.233508183427436</v>
+        <v>0.2290621438102584</v>
       </c>
       <c r="J4" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="K4" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08754244625845897</v>
+        <v>0.08457690728517409</v>
       </c>
       <c r="M4" t="n">
-        <v>4.64702711901517</v>
+        <v>4.654598077713906</v>
       </c>
       <c r="N4" t="n">
-        <v>31.4876409294788</v>
+        <v>31.57389939427111</v>
       </c>
       <c r="O4" t="n">
-        <v>5.611384938629572</v>
+        <v>5.619065704747642</v>
       </c>
       <c r="P4" t="n">
-        <v>339.6401253652668</v>
+        <v>339.6873326464834</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39962,28 +40072,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2884343384939473</v>
+        <v>0.2835186250218981</v>
       </c>
       <c r="J5" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="K5" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="L5" t="n">
-        <v>0.121308829883067</v>
+        <v>0.1176830763894039</v>
       </c>
       <c r="M5" t="n">
-        <v>4.59030752555635</v>
+        <v>4.599413541998205</v>
       </c>
       <c r="N5" t="n">
-        <v>33.38717662840645</v>
+        <v>33.50620951797223</v>
       </c>
       <c r="O5" t="n">
-        <v>5.778163776530262</v>
+        <v>5.78845484719128</v>
       </c>
       <c r="P5" t="n">
-        <v>341.1875514556394</v>
+        <v>341.2397464131129</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -40040,28 +40150,28 @@
         <v>0.1235</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2689596884418558</v>
+        <v>0.2646326545339632</v>
       </c>
       <c r="J6" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="K6" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0978115091809274</v>
+        <v>0.09514363777951973</v>
       </c>
       <c r="M6" t="n">
-        <v>5.098474080147225</v>
+        <v>5.107572684136987</v>
       </c>
       <c r="N6" t="n">
-        <v>36.79042117711036</v>
+        <v>36.85138699110431</v>
       </c>
       <c r="O6" t="n">
-        <v>6.06551079276184</v>
+        <v>6.070534325008327</v>
       </c>
       <c r="P6" t="n">
-        <v>345.3978181569139</v>
+        <v>345.4439178775394</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -40118,28 +40228,28 @@
         <v>0.1494</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1592400920765321</v>
+        <v>0.1570315837024897</v>
       </c>
       <c r="J7" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="K7" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="L7" t="n">
-        <v>0.054835059276515</v>
+        <v>0.0536339241679219</v>
       </c>
       <c r="M7" t="n">
-        <v>4.092989907305794</v>
+        <v>4.09235069013267</v>
       </c>
       <c r="N7" t="n">
-        <v>24.21564536451796</v>
+        <v>24.19051569845236</v>
       </c>
       <c r="O7" t="n">
-        <v>4.920939479867433</v>
+        <v>4.918385476805612</v>
       </c>
       <c r="P7" t="n">
-        <v>355.0985593410024</v>
+        <v>355.1220090637356</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -40196,28 +40306,28 @@
         <v>0.1153</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1577164912467607</v>
+        <v>0.159490511449056</v>
       </c>
       <c r="J8" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="K8" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03847224805025484</v>
+        <v>0.03951603822558536</v>
       </c>
       <c r="M8" t="n">
-        <v>4.618795914751535</v>
+        <v>4.612713781651999</v>
       </c>
       <c r="N8" t="n">
-        <v>34.44374725946957</v>
+        <v>34.37462248088659</v>
       </c>
       <c r="O8" t="n">
-        <v>5.868879557417205</v>
+        <v>5.862987504752725</v>
       </c>
       <c r="P8" t="n">
-        <v>363.0414828931261</v>
+        <v>363.022645262441</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -40274,28 +40384,28 @@
         <v>0.1881</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1044418042341779</v>
+        <v>0.1062267658787051</v>
       </c>
       <c r="J9" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="K9" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02543523644494006</v>
+        <v>0.02641942818847431</v>
       </c>
       <c r="M9" t="n">
-        <v>3.849764065219815</v>
+        <v>3.847781449760519</v>
       </c>
       <c r="N9" t="n">
-        <v>23.15610862976864</v>
+        <v>23.11894006803658</v>
       </c>
       <c r="O9" t="n">
-        <v>4.812079449652576</v>
+        <v>4.808215892411298</v>
       </c>
       <c r="P9" t="n">
-        <v>360.1262741935713</v>
+        <v>360.1073209064615</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -40352,28 +40462,28 @@
         <v>0.1177</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1021929725760601</v>
+        <v>0.1089180604354924</v>
       </c>
       <c r="J10" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="K10" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01607200813119636</v>
+        <v>0.01812951781387218</v>
       </c>
       <c r="M10" t="n">
-        <v>4.959454252643008</v>
+        <v>4.98161716303584</v>
       </c>
       <c r="N10" t="n">
-        <v>35.42233270152654</v>
+        <v>35.72064267288547</v>
       </c>
       <c r="O10" t="n">
-        <v>5.951666380227183</v>
+        <v>5.976674884322007</v>
       </c>
       <c r="P10" t="n">
-        <v>354.0030861785815</v>
+        <v>353.9316781455374</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -40430,28 +40540,28 @@
         <v>0.1328</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1795092171128366</v>
+        <v>0.1869688057258715</v>
       </c>
       <c r="J11" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="K11" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0465785802004447</v>
+        <v>0.04999464762263128</v>
       </c>
       <c r="M11" t="n">
-        <v>4.907188742199764</v>
+        <v>4.92897211960221</v>
       </c>
       <c r="N11" t="n">
-        <v>36.54383196022166</v>
+        <v>36.93111022502395</v>
       </c>
       <c r="O11" t="n">
-        <v>6.045149457227808</v>
+        <v>6.077097187393332</v>
       </c>
       <c r="P11" t="n">
-        <v>343.11168235886</v>
+        <v>343.0324761082419</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -40508,28 +40618,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2036164079499035</v>
+        <v>0.2081188592574774</v>
       </c>
       <c r="J12" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="K12" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06985108079723801</v>
+        <v>0.07277846287642165</v>
       </c>
       <c r="M12" t="n">
-        <v>4.428163797419832</v>
+        <v>4.433032109874429</v>
       </c>
       <c r="N12" t="n">
-        <v>30.58769985638888</v>
+        <v>30.67997636435023</v>
       </c>
       <c r="O12" t="n">
-        <v>5.530614781051821</v>
+        <v>5.538950836065458</v>
       </c>
       <c r="P12" t="n">
-        <v>341.6573635197565</v>
+        <v>341.6095554292925</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -40567,7 +40677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M709"/>
+  <dimension ref="A1:M711"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88069,6 +88179,140 @@
         </is>
       </c>
     </row>
+    <row r="710">
+      <c r="A710" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-08 21:59:26+00:00</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>-37.14538161364889,175.87942489123608</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>-37.14609935567663,175.8794672440639</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>-37.146809974058705,175.87957651738333</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>-37.14751635088497,175.87970374309734</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>-37.1482209618349,175.87983140081997</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>-37.14892616976602,175.88000627071278</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>-37.149623740850366,175.88022493614844</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>-37.150319877303424,175.8803538003529</t>
+        </is>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>-37.150994794528174,175.88063967177496</t>
+        </is>
+      </c>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>-37.15169552274184,175.8808380998374</t>
+        </is>
+      </c>
+      <c r="L710" t="inlineStr">
+        <is>
+          <t>-37.15238397160643,175.8810983529541</t>
+        </is>
+      </c>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:59:37+00:00</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>-37.14538123407787,175.87942846032024</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>-37.14609754084553,175.8794843089071</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>-37.14680859809659,175.87958945555295</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>-37.14751555913758,175.87971201039926</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>-37.1482199244643,175.87984540574135</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>-37.14892583783534,175.88001154282605</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>-37.14962301903749,175.8802309449481</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>-37.150319499131946,175.88035553759693</t>
+        </is>
+      </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>-37.15099524984487,175.8806379636425</t>
+        </is>
+      </c>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>-37.151697984446194,175.88082999973307</t>
+        </is>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>-37.152383453381184,175.88109991171066</t>
+        </is>
+      </c>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0192/nzd0192.xlsx
+++ b/data/nzd0192/nzd0192.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M711"/>
+  <dimension ref="A1:M716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32441,6 +32441,231 @@
         <v>355.17</v>
       </c>
       <c r="M711" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 21:59:24+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>342.53</v>
+      </c>
+      <c r="C712" t="n">
+        <v>338.26</v>
+      </c>
+      <c r="D712" t="n">
+        <v>339.28</v>
+      </c>
+      <c r="E712" t="n">
+        <v>341.08</v>
+      </c>
+      <c r="F712" t="n">
+        <v>346.33</v>
+      </c>
+      <c r="G712" t="n">
+        <v>356.15</v>
+      </c>
+      <c r="H712" t="n">
+        <v>370.71</v>
+      </c>
+      <c r="I712" t="n">
+        <v>366.09</v>
+      </c>
+      <c r="J712" t="n">
+        <v>367.76</v>
+      </c>
+      <c r="K712" t="n">
+        <v>359.72</v>
+      </c>
+      <c r="L712" t="n">
+        <v>355.08</v>
+      </c>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>342.51</v>
+      </c>
+      <c r="C713" t="n">
+        <v>338.21</v>
+      </c>
+      <c r="D713" t="n">
+        <v>338.04</v>
+      </c>
+      <c r="E713" t="n">
+        <v>341.05</v>
+      </c>
+      <c r="F713" t="n">
+        <v>346.63</v>
+      </c>
+      <c r="G713" t="n">
+        <v>355.85</v>
+      </c>
+      <c r="H713" t="n">
+        <v>369.27</v>
+      </c>
+      <c r="I713" t="n">
+        <v>365.71</v>
+      </c>
+      <c r="J713" t="n">
+        <v>365.53</v>
+      </c>
+      <c r="K713" t="n">
+        <v>358.4</v>
+      </c>
+      <c r="L713" t="n">
+        <v>354.2</v>
+      </c>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>341.28</v>
+      </c>
+      <c r="C714" t="n">
+        <v>337.91</v>
+      </c>
+      <c r="D714" t="n">
+        <v>337.45</v>
+      </c>
+      <c r="E714" t="n">
+        <v>341.35</v>
+      </c>
+      <c r="F714" t="n">
+        <v>347.21</v>
+      </c>
+      <c r="G714" t="n">
+        <v>355.87</v>
+      </c>
+      <c r="H714" t="n">
+        <v>368.38</v>
+      </c>
+      <c r="I714" t="n">
+        <v>365.17</v>
+      </c>
+      <c r="J714" t="n">
+        <v>364.27</v>
+      </c>
+      <c r="K714" t="n">
+        <v>357.6</v>
+      </c>
+      <c r="L714" t="n">
+        <v>354.22</v>
+      </c>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:59:13+00:00</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>340.19</v>
+      </c>
+      <c r="C715" t="n">
+        <v>337.39</v>
+      </c>
+      <c r="D715" t="n">
+        <v>337.34</v>
+      </c>
+      <c r="E715" t="n">
+        <v>341.76</v>
+      </c>
+      <c r="F715" t="n">
+        <v>347.07</v>
+      </c>
+      <c r="G715" t="n">
+        <v>355.97</v>
+      </c>
+      <c r="H715" t="n">
+        <v>368.21</v>
+      </c>
+      <c r="I715" t="n">
+        <v>364.82</v>
+      </c>
+      <c r="J715" t="n">
+        <v>363.24</v>
+      </c>
+      <c r="K715" t="n">
+        <v>357</v>
+      </c>
+      <c r="L715" t="n">
+        <v>353.89</v>
+      </c>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>339.57</v>
+      </c>
+      <c r="C716" t="n">
+        <v>337.36</v>
+      </c>
+      <c r="D716" t="n">
+        <v>337.9</v>
+      </c>
+      <c r="E716" t="n">
+        <v>341.6</v>
+      </c>
+      <c r="F716" t="n">
+        <v>347.22</v>
+      </c>
+      <c r="G716" t="n">
+        <v>355.82</v>
+      </c>
+      <c r="H716" t="n">
+        <v>368.44</v>
+      </c>
+      <c r="I716" t="n">
+        <v>364.8</v>
+      </c>
+      <c r="J716" t="n">
+        <v>362.66</v>
+      </c>
+      <c r="K716" t="n">
+        <v>356.68</v>
+      </c>
+      <c r="L716" t="n">
+        <v>353.6</v>
+      </c>
+      <c r="M716" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32457,7 +32682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B721"/>
+  <dimension ref="A1:B726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39670,6 +39895,56 @@
       </c>
       <c r="B721" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-04-24 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>-0.53</v>
       </c>
     </row>
   </sheetData>
@@ -39838,28 +40113,28 @@
         <v>0.1845</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1590508125134256</v>
+        <v>0.1568002161582532</v>
       </c>
       <c r="J2" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="K2" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05223360309977332</v>
+        <v>0.05154694981280306</v>
       </c>
       <c r="M2" t="n">
-        <v>4.03397620957326</v>
+        <v>4.016222541236133</v>
       </c>
       <c r="N2" t="n">
-        <v>25.51964456876823</v>
+        <v>25.36922489682724</v>
       </c>
       <c r="O2" t="n">
-        <v>5.0516971968605</v>
+        <v>5.036787160167406</v>
       </c>
       <c r="P2" t="n">
-        <v>338.5706750563825</v>
+        <v>338.594675457496</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -39916,28 +40191,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3227420940350684</v>
+        <v>0.3151478809467744</v>
       </c>
       <c r="J3" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="K3" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1160116229044259</v>
+        <v>0.1123042897077405</v>
       </c>
       <c r="M3" t="n">
-        <v>5.513539166757207</v>
+        <v>5.511791186312042</v>
       </c>
       <c r="N3" t="n">
-        <v>44.12734446104924</v>
+        <v>44.02481879026888</v>
       </c>
       <c r="O3" t="n">
-        <v>6.64284159536032</v>
+        <v>6.635120103680783</v>
       </c>
       <c r="P3" t="n">
-        <v>334.6483346441076</v>
+        <v>334.729261723024</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39994,28 +40269,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2290621438102584</v>
+        <v>0.2182064796475936</v>
       </c>
       <c r="J4" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="K4" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08457690728517409</v>
+        <v>0.0775183483792522</v>
       </c>
       <c r="M4" t="n">
-        <v>4.654598077713906</v>
+        <v>4.671959797714535</v>
       </c>
       <c r="N4" t="n">
-        <v>31.57389939427111</v>
+        <v>31.77529052769174</v>
       </c>
       <c r="O4" t="n">
-        <v>5.619065704747642</v>
+        <v>5.636957559507765</v>
       </c>
       <c r="P4" t="n">
-        <v>339.6873326464834</v>
+        <v>339.8030172368987</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -40072,28 +40347,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2835186250218981</v>
+        <v>0.2731525606862236</v>
       </c>
       <c r="J5" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="K5" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1176830763894039</v>
+        <v>0.110579740382278</v>
       </c>
       <c r="M5" t="n">
-        <v>4.599413541998205</v>
+        <v>4.615081885384141</v>
       </c>
       <c r="N5" t="n">
-        <v>33.50620951797223</v>
+        <v>33.65449071690735</v>
       </c>
       <c r="O5" t="n">
-        <v>5.78845484719128</v>
+        <v>5.801249065236499</v>
       </c>
       <c r="P5" t="n">
-        <v>341.2397464131129</v>
+        <v>341.3501993796133</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -40150,28 +40425,28 @@
         <v>0.1235</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2646326545339632</v>
+        <v>0.2567671779161307</v>
       </c>
       <c r="J6" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="K6" t="n">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09514363777951973</v>
+        <v>0.09087291594210078</v>
       </c>
       <c r="M6" t="n">
-        <v>5.107572684136987</v>
+        <v>5.114126610013767</v>
       </c>
       <c r="N6" t="n">
-        <v>36.85138699110431</v>
+        <v>36.81261860975177</v>
       </c>
       <c r="O6" t="n">
-        <v>6.070534325008327</v>
+        <v>6.067340324207286</v>
       </c>
       <c r="P6" t="n">
-        <v>345.4439178775394</v>
+        <v>345.5280069949562</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -40228,28 +40503,28 @@
         <v>0.1494</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1570315837024897</v>
+        <v>0.1523139948834503</v>
       </c>
       <c r="J7" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="K7" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0536339241679219</v>
+        <v>0.05121768577007779</v>
       </c>
       <c r="M7" t="n">
-        <v>4.09235069013267</v>
+        <v>4.087021934578756</v>
       </c>
       <c r="N7" t="n">
-        <v>24.19051569845236</v>
+        <v>24.10056732039503</v>
       </c>
       <c r="O7" t="n">
-        <v>4.918385476805612</v>
+        <v>4.909232864755452</v>
       </c>
       <c r="P7" t="n">
-        <v>355.1220090637356</v>
+        <v>355.1722797235317</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -40306,28 +40581,28 @@
         <v>0.1153</v>
       </c>
       <c r="I8" t="n">
-        <v>0.159490511449056</v>
+        <v>0.1618483759208507</v>
       </c>
       <c r="J8" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="K8" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03951603822558536</v>
+        <v>0.04122986749387669</v>
       </c>
       <c r="M8" t="n">
-        <v>4.612713781651999</v>
+        <v>4.589543246178137</v>
       </c>
       <c r="N8" t="n">
-        <v>34.37462248088659</v>
+        <v>34.16018922570733</v>
       </c>
       <c r="O8" t="n">
-        <v>5.862987504752725</v>
+        <v>5.844671866384574</v>
       </c>
       <c r="P8" t="n">
-        <v>363.022645262441</v>
+        <v>362.9975370013248</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -40384,28 +40659,28 @@
         <v>0.1881</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1062267658787051</v>
+        <v>0.1094997619239195</v>
       </c>
       <c r="J9" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="K9" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02641942818847431</v>
+        <v>0.02840771163016997</v>
       </c>
       <c r="M9" t="n">
-        <v>3.847781449760519</v>
+        <v>3.836982393365955</v>
       </c>
       <c r="N9" t="n">
-        <v>23.11894006803658</v>
+        <v>22.99721137192644</v>
       </c>
       <c r="O9" t="n">
-        <v>4.808215892411298</v>
+        <v>4.795540779925288</v>
       </c>
       <c r="P9" t="n">
-        <v>360.1073209064615</v>
+        <v>360.0724539765898</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -40462,28 +40737,28 @@
         <v>0.1177</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1089180604354924</v>
+        <v>0.1197815483612238</v>
       </c>
       <c r="J10" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="K10" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01812951781387218</v>
+        <v>0.02191254008485743</v>
       </c>
       <c r="M10" t="n">
-        <v>4.98161716303584</v>
+        <v>5.004656748954091</v>
       </c>
       <c r="N10" t="n">
-        <v>35.72064267288547</v>
+        <v>35.91416978082651</v>
       </c>
       <c r="O10" t="n">
-        <v>5.976674884322007</v>
+        <v>5.992843213436049</v>
       </c>
       <c r="P10" t="n">
-        <v>353.9316781455374</v>
+        <v>353.8159538562059</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -40540,28 +40815,28 @@
         <v>0.1328</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1869688057258715</v>
+        <v>0.2006013135750911</v>
       </c>
       <c r="J11" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="K11" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04999464762263128</v>
+        <v>0.05698811211025412</v>
       </c>
       <c r="M11" t="n">
-        <v>4.92897211960221</v>
+        <v>4.959412585024442</v>
       </c>
       <c r="N11" t="n">
-        <v>36.93111022502395</v>
+        <v>37.34233419929149</v>
       </c>
       <c r="O11" t="n">
-        <v>6.077097187393332</v>
+        <v>6.110837438460583</v>
       </c>
       <c r="P11" t="n">
-        <v>343.0324761082419</v>
+        <v>342.8872331294193</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -40618,28 +40893,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2081188592574774</v>
+        <v>0.2178330302558237</v>
       </c>
       <c r="J12" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="K12" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07277846287642165</v>
+        <v>0.07951939636926697</v>
       </c>
       <c r="M12" t="n">
-        <v>4.433032109874429</v>
+        <v>4.439041369948717</v>
       </c>
       <c r="N12" t="n">
-        <v>30.67997636435023</v>
+        <v>30.80278974328475</v>
       </c>
       <c r="O12" t="n">
-        <v>5.538950836065458</v>
+        <v>5.550026102937243</v>
       </c>
       <c r="P12" t="n">
-        <v>341.6095554292925</v>
+        <v>341.5060538428623</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -40677,7 +40952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M711"/>
+  <dimension ref="A1:M716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88313,6 +88588,341 @@
         </is>
       </c>
     </row>
+    <row r="712">
+      <c r="A712" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 21:59:24+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>-37.145380854506755,175.87943202940434</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>-37.146097445952336,175.8794852011865</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>-37.14680775591221,175.87959737460474</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>-37.147514981375615,175.87971804329513</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>-37.1482192854432,175.87985403277267</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>-37.14892549884208,175.8800169271119</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>-37.149622978936776,175.8802312787703</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>-37.15031968821769,175.88035466897492</t>
+        </is>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>-37.150997640257174,175.88062899594678</t>
+        </is>
+      </c>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>-37.1517013413149,175.88081895413532</t>
+        </is>
+      </c>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>-37.15238376431633,175.8810989764567</t>
+        </is>
+      </c>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>-37.14538087822995,175.87943180633658</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>-37.14609750526058,175.8794846435119</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>-37.146809226769115,175.87958354414792</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>-37.147515013473516,175.87971770813425</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>-37.148219036473755,175.87985739395367</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>-37.148925710712895,175.88001356193325</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>-37.14962490377044,175.88021525530425</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>-37.150320586374846,175.88035054302037</t>
+        </is>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>-37.1510039862295,175.8806051888468</t>
+        </is>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>-37.151705561376986,175.8808050682395</t>
+        </is>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>-37.15238680457079,175.88108983175132</t>
+        </is>
+      </c>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>-37.145382337205824,175.8794180876693</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>-37.146097861110015,175.87948129746425</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>-37.14680992661176,175.87957696352711</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>-37.14751469249452,175.87972105974302</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>-37.148218555132594,175.87986389223684</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>-37.14892569658818,175.8800137862785</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>-37.14962609342351,175.88020535191154</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>-37.1503218627032,175.8803446798216</t>
+        </is>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>-37.151007571844104,175.88059173729968</t>
+        </is>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>-37.15170811898961,175.8807966525443</t>
+        </is>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>-37.15238673547411,175.88109003958556</t>
+        </is>
+      </c>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:59:13+00:00</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>-37.1453836301181,175.87940593047583</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>-37.14609847791549,175.87947549764831</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>-37.14681005709086,175.8795757366317</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>-37.14751425382308,175.87972564027493</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>-37.14821867131843,175.87986232368576</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>-37.14892562596457,175.88001490800474</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>-37.14962632066052,175.88020346025223</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>-37.150322689952915,175.88034087960008</t>
+        </is>
+      </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>-37.151010502940665,175.88058074119266</t>
+        </is>
+      </c>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>-37.15171003719872,175.8807903407725</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>-37.15238787556936,175.88108661032084</t>
+        </is>
+      </c>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>-37.14538436553552,175.87939901537473</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>-37.1460985135004,175.87947516304354</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>-37.14680939283352,175.8795819826447</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>-37.147514425011956,175.8797238527503</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>-37.14821854683361,175.87986400427621</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>-37.14892573189997,175.8800132254154</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>-37.1496260132222,175.880206019556</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>-37.15032273722432,175.88034066244455</t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>-37.15101215346062,175.88057454920965</t>
+        </is>
+      </c>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>-37.151711060243436,175.88078697449407</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>-37.152388877471175,175.8810835967245</t>
+        </is>
+      </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0192/nzd0192.xlsx
+++ b/data/nzd0192/nzd0192.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M716"/>
+  <dimension ref="A1:M720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32666,6 +32666,186 @@
         <v>353.6</v>
       </c>
       <c r="M716" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:05:07+00:00</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>337.28</v>
+      </c>
+      <c r="C717" t="n">
+        <v>336.15</v>
+      </c>
+      <c r="D717" t="n">
+        <v>336.3</v>
+      </c>
+      <c r="E717" t="n">
+        <v>340.47</v>
+      </c>
+      <c r="F717" t="n">
+        <v>345.32</v>
+      </c>
+      <c r="G717" t="n">
+        <v>355.8</v>
+      </c>
+      <c r="H717" t="n">
+        <v>367.9</v>
+      </c>
+      <c r="I717" t="n">
+        <v>364.26</v>
+      </c>
+      <c r="J717" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="K717" t="n">
+        <v>354.32</v>
+      </c>
+      <c r="L717" t="n">
+        <v>352.01</v>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
+        <v>337.33</v>
+      </c>
+      <c r="C718" t="n">
+        <v>336.71</v>
+      </c>
+      <c r="D718" t="n">
+        <v>337.4</v>
+      </c>
+      <c r="E718" t="n">
+        <v>340.91</v>
+      </c>
+      <c r="F718" t="n">
+        <v>345.94</v>
+      </c>
+      <c r="G718" t="n">
+        <v>356.24</v>
+      </c>
+      <c r="H718" t="n">
+        <v>368.52</v>
+      </c>
+      <c r="I718" t="n">
+        <v>364.47</v>
+      </c>
+      <c r="J718" t="n">
+        <v>361.59</v>
+      </c>
+      <c r="K718" t="n">
+        <v>355.43</v>
+      </c>
+      <c r="L718" t="n">
+        <v>353.44</v>
+      </c>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-19 21:59:15+00:00</t>
+        </is>
+      </c>
+      <c r="B719" t="n">
+        <v>337</v>
+      </c>
+      <c r="C719" t="n">
+        <v>336.45</v>
+      </c>
+      <c r="D719" t="n">
+        <v>336.87</v>
+      </c>
+      <c r="E719" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="F719" t="n">
+        <v>345.68</v>
+      </c>
+      <c r="G719" t="n">
+        <v>356.45</v>
+      </c>
+      <c r="H719" t="n">
+        <v>368.87</v>
+      </c>
+      <c r="I719" t="n">
+        <v>364.4</v>
+      </c>
+      <c r="J719" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="K719" t="n">
+        <v>355.47</v>
+      </c>
+      <c r="L719" t="n">
+        <v>353.8</v>
+      </c>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>335.77</v>
+      </c>
+      <c r="C720" t="n">
+        <v>336.07</v>
+      </c>
+      <c r="D720" t="n">
+        <v>337.74</v>
+      </c>
+      <c r="E720" t="n">
+        <v>340.45</v>
+      </c>
+      <c r="F720" t="n">
+        <v>345.14</v>
+      </c>
+      <c r="G720" t="n">
+        <v>355.8</v>
+      </c>
+      <c r="H720" t="n">
+        <v>369.07</v>
+      </c>
+      <c r="I720" t="n">
+        <v>363.72</v>
+      </c>
+      <c r="J720" t="n">
+        <v>359.72</v>
+      </c>
+      <c r="K720" t="n">
+        <v>354.08</v>
+      </c>
+      <c r="L720" t="n">
+        <v>353.26</v>
+      </c>
+      <c r="M720" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32682,7 +32862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B726"/>
+  <dimension ref="A1:B730"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39945,6 +40125,46 @@
       </c>
       <c r="B726" t="n">
         <v>-0.53</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-06-19 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>-0.66</v>
       </c>
     </row>
   </sheetData>
@@ -40113,28 +40333,28 @@
         <v>0.1845</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1568002161582532</v>
+        <v>0.1502426781482964</v>
       </c>
       <c r="J2" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="K2" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05154694981280306</v>
+        <v>0.04773545837564652</v>
       </c>
       <c r="M2" t="n">
-        <v>4.016222541236133</v>
+        <v>4.024608138014805</v>
       </c>
       <c r="N2" t="n">
-        <v>25.36922489682724</v>
+        <v>25.42504507273517</v>
       </c>
       <c r="O2" t="n">
-        <v>5.036787160167406</v>
+        <v>5.042325363632851</v>
       </c>
       <c r="P2" t="n">
-        <v>338.594675457496</v>
+        <v>338.6648203678432</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -40191,28 +40411,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3151478809467744</v>
+        <v>0.3076079028815945</v>
       </c>
       <c r="J3" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="K3" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1123042897077405</v>
+        <v>0.1081930357982409</v>
       </c>
       <c r="M3" t="n">
-        <v>5.511791186312042</v>
+        <v>5.517281019454903</v>
       </c>
       <c r="N3" t="n">
-        <v>44.02481879026888</v>
+        <v>44.03774910219619</v>
       </c>
       <c r="O3" t="n">
-        <v>6.635120103680783</v>
+        <v>6.636094416311162</v>
       </c>
       <c r="P3" t="n">
-        <v>334.729261723024</v>
+        <v>334.8099087217884</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -40269,28 +40489,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2182064796475936</v>
+        <v>0.2087636366742749</v>
       </c>
       <c r="J4" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="K4" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0775183483792522</v>
+        <v>0.0713989499463239</v>
       </c>
       <c r="M4" t="n">
-        <v>4.671959797714535</v>
+        <v>4.688875812236376</v>
       </c>
       <c r="N4" t="n">
-        <v>31.77529052769174</v>
+        <v>32.00410123256284</v>
       </c>
       <c r="O4" t="n">
-        <v>5.636957559507765</v>
+        <v>5.657216739047819</v>
       </c>
       <c r="P4" t="n">
-        <v>339.8030172368987</v>
+        <v>339.9040111787214</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -40347,28 +40567,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2731525606862236</v>
+        <v>0.2643990716753497</v>
       </c>
       <c r="J5" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="K5" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="L5" t="n">
-        <v>0.110579740382278</v>
+        <v>0.1045261843717604</v>
       </c>
       <c r="M5" t="n">
-        <v>4.615081885384141</v>
+        <v>4.631479357011838</v>
       </c>
       <c r="N5" t="n">
-        <v>33.65449071690735</v>
+        <v>33.81475369636112</v>
       </c>
       <c r="O5" t="n">
-        <v>5.801249065236499</v>
+        <v>5.815045459526616</v>
       </c>
       <c r="P5" t="n">
-        <v>341.3501993796133</v>
+        <v>341.4438249149053</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -40425,28 +40645,28 @@
         <v>0.1235</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2567671779161307</v>
+        <v>0.249140173137282</v>
       </c>
       <c r="J6" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="K6" t="n">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09087291594210078</v>
+        <v>0.08642798487341652</v>
       </c>
       <c r="M6" t="n">
-        <v>5.114126610013767</v>
+        <v>5.126309357885348</v>
       </c>
       <c r="N6" t="n">
-        <v>36.81261860975177</v>
+        <v>36.86970440617738</v>
       </c>
       <c r="O6" t="n">
-        <v>6.067340324207286</v>
+        <v>6.07204285279488</v>
       </c>
       <c r="P6" t="n">
-        <v>345.5280069949562</v>
+        <v>345.6098599780461</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -40503,28 +40723,28 @@
         <v>0.1494</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1523139948834503</v>
+        <v>0.1488040439443479</v>
       </c>
       <c r="J7" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="K7" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05121768577007779</v>
+        <v>0.04946886792078509</v>
       </c>
       <c r="M7" t="n">
-        <v>4.087021934578756</v>
+        <v>4.081709764918013</v>
       </c>
       <c r="N7" t="n">
-        <v>24.10056732039503</v>
+        <v>24.02273353075986</v>
       </c>
       <c r="O7" t="n">
-        <v>4.909232864755452</v>
+        <v>4.901299167645234</v>
       </c>
       <c r="P7" t="n">
-        <v>355.1722797235317</v>
+        <v>355.2098211624607</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -40581,28 +40801,28 @@
         <v>0.1153</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1618483759208507</v>
+        <v>0.1632091947090029</v>
       </c>
       <c r="J8" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="K8" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04122986749387669</v>
+        <v>0.04238578865606479</v>
       </c>
       <c r="M8" t="n">
-        <v>4.589543246178137</v>
+        <v>4.569168617132386</v>
       </c>
       <c r="N8" t="n">
-        <v>34.16018922570733</v>
+        <v>33.97959048005498</v>
       </c>
       <c r="O8" t="n">
-        <v>5.844671866384574</v>
+        <v>5.829201530231647</v>
       </c>
       <c r="P8" t="n">
-        <v>362.9975370013248</v>
+        <v>362.9829766307603</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -40659,28 +40879,28 @@
         <v>0.1881</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1094997619239195</v>
+        <v>0.1108095813895328</v>
       </c>
       <c r="J9" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="K9" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02840771163016997</v>
+        <v>0.02941293815543977</v>
       </c>
       <c r="M9" t="n">
-        <v>3.836982393365955</v>
+        <v>3.822020534569166</v>
       </c>
       <c r="N9" t="n">
-        <v>22.99721137192644</v>
+        <v>22.8775387074784</v>
       </c>
       <c r="O9" t="n">
-        <v>4.795540779925288</v>
+        <v>4.783047010795357</v>
       </c>
       <c r="P9" t="n">
-        <v>360.0724539765898</v>
+        <v>360.0584466522079</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -40737,28 +40957,28 @@
         <v>0.1177</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1197815483612238</v>
+        <v>0.1240976849326437</v>
       </c>
       <c r="J10" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="K10" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02191254008485743</v>
+        <v>0.0237115012142699</v>
       </c>
       <c r="M10" t="n">
-        <v>5.004656748954091</v>
+        <v>4.999722198225136</v>
       </c>
       <c r="N10" t="n">
-        <v>35.91416978082651</v>
+        <v>35.80181665780927</v>
       </c>
       <c r="O10" t="n">
-        <v>5.992843213436049</v>
+        <v>5.983461929168537</v>
       </c>
       <c r="P10" t="n">
-        <v>353.8159538562059</v>
+        <v>353.7697955117839</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -40815,28 +41035,28 @@
         <v>0.1328</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2006013135750911</v>
+        <v>0.2077878869661772</v>
       </c>
       <c r="J11" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="K11" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05698811211025412</v>
+        <v>0.06123824881397888</v>
       </c>
       <c r="M11" t="n">
-        <v>4.959412585024442</v>
+        <v>4.965919743762958</v>
       </c>
       <c r="N11" t="n">
-        <v>37.34233419929149</v>
+        <v>37.37073668987897</v>
       </c>
       <c r="O11" t="n">
-        <v>6.110837438460583</v>
+        <v>6.113160940943643</v>
       </c>
       <c r="P11" t="n">
-        <v>342.8872331294193</v>
+        <v>342.8103675696757</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -40893,28 +41113,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2178330302558237</v>
+        <v>0.2241580873982636</v>
       </c>
       <c r="J12" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="K12" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07951939636926697</v>
+        <v>0.08430532696056725</v>
       </c>
       <c r="M12" t="n">
-        <v>4.439041369948717</v>
+        <v>4.438656884122985</v>
       </c>
       <c r="N12" t="n">
-        <v>30.80278974328475</v>
+        <v>30.81506426928226</v>
       </c>
       <c r="O12" t="n">
-        <v>5.550026102937243</v>
+        <v>5.551131800748588</v>
       </c>
       <c r="P12" t="n">
-        <v>341.5060538428623</v>
+        <v>341.4383963637854</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -40952,7 +41172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M716"/>
+  <dimension ref="A1:M720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88923,6 +89143,274 @@
         </is>
       </c>
     </row>
+    <row r="717">
+      <c r="A717" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:05:07+00:00</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>-37.145387081831956,175.87937347411278</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>-37.146099948758156,175.8794616673175</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>-37.146811290710794,175.87956413689292</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>-37.147515634032644,175.8797112283572</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>-37.148220123639575,175.87984271679647</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>-37.148925746024695,175.88001300107015</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>-37.14962673503382,175.8802000107558</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>-37.15032401355221,175.88033479924542</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>-37.15101630821637,175.8805589624926</t>
+        </is>
+      </c>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>-37.1517186051954,175.8807621481876</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>-37.15239437065566,175.8810670739016</t>
+        </is>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>-37.14538702252422,175.87937403178228</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>-37.14609928450684,175.87946791327343</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>-37.14680998592044,175.8795764058474</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>-37.147515163263684,175.87971614405015</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>-37.148219609103315,175.87984966323737</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>-37.148925435280816,175.8800179366655</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>-37.14962590628713,175.88020690974864</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>-37.1503235172025,175.88033707937845</t>
+        </is>
+      </c>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>-37.15101519838455,175.88056312606787</t>
+        </is>
+      </c>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>-37.15171505651098,175.880773824968</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>-37.152389430244554,175.8810819340506</t>
+        </is>
+      </c>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-19 21:59:15+00:00</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>-37.14538741395516,175.87937035116357</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>-37.146099592909266,175.87946501336535</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>-37.14681061459231,175.8795704944421</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>-37.14751495997702,175.8797182667357</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>-37.14821982487664,175.87984675021377</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>-37.148925286971156,175.88002029229054</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>-37.14962543844607,175.8802108043413</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>-37.150323682652406,175.8803363193341</t>
+        </is>
+      </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>-37.15101585290077,175.88056067062604</t>
+        </is>
+      </c>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>-37.15171492863044,175.88077424575286</t>
+        </is>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>-37.15238818650441,175.8810856750668</t>
+        </is>
+      </c>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>-37.145388872924,175.87935663249348</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>-37.14610004365118,175.87946077503807</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>-37.14680958262136,175.87958019806956</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>-37.147515655431214,175.8797110049166</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>-37.148220273021,175.8798407000878</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>-37.148925746024695,175.88001300107015</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>-37.14962517110828,175.88021302982276</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>-37.15032528987979,175.88032893604608</t>
+        </is>
+      </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>-37.151020519884554,175.88054316225694</t>
+        </is>
+      </c>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>-37.15171937247836,175.8807596234782</t>
+        </is>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>-37.152390052114576,175.88108006354244</t>
+        </is>
+      </c>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
